--- a/Exercício_Finanças_Aluno.xlsx
+++ b/Exercício_Finanças_Aluno.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pichau\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21F3AC2-069B-4CB3-8C8B-2FD2D24EC381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31465CF2-A724-4207-9668-F32A95D4A575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aluno" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="37">
   <si>
     <t>Utilize fórmulas para realizar os cálculos</t>
   </si>
@@ -111,29 +109,54 @@
     <t>Março</t>
   </si>
   <si>
-    <t xml:space="preserve">Janeiro </t>
-  </si>
-  <si>
     <t>Salário</t>
   </si>
   <si>
-    <t>Despesas</t>
-  </si>
-  <si>
     <t>Transporte</t>
   </si>
   <si>
     <t>Telefone</t>
   </si>
   <si>
-    <t>Reajustes</t>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>Outras</t>
+  </si>
+  <si>
+    <t>Ong</t>
+  </si>
+  <si>
+    <t>Desp/Extras</t>
+  </si>
+  <si>
+    <t>Total/Desp</t>
+  </si>
+  <si>
+    <t>Sobra</t>
+  </si>
+  <si>
+    <t>Saldo Acmld</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>Junho</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -167,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,13 +199,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,7 +249,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -220,32 +267,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,240 +594,576 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" customWidth="1"/>
-    <col min="2" max="7" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.42578125" style="1"/>
+    <col min="2" max="2" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="1"/>
+    <col min="10" max="10" width="12" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" style="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" style="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="10.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="38"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="32"/>
+      <c r="J15" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="29"/>
+      <c r="M15" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15" s="26"/>
+      <c r="P15" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q15" s="23"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="16"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="B16" s="20">
+        <v>1700</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="20">
+        <v>1700</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="22">
+        <v>1700</v>
+      </c>
+      <c r="I16" s="22"/>
+      <c r="J16" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="22">
+        <f>B16*(1+10%)</f>
+        <v>1870.0000000000002</v>
+      </c>
+      <c r="M16" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="22">
+        <f>B16*(1+10%)</f>
+        <v>1870.0000000000002</v>
+      </c>
+      <c r="P16" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="22">
+        <f>B16*(1+10%)</f>
+        <v>1870.0000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="19">
-        <v>1700</v>
-      </c>
-      <c r="E18" s="21" t="s">
+      <c r="B17" s="20">
+        <v>196</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="D17" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="16">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="16"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="E17" s="20">
+        <v>196</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="22">
+        <f>B17*(1+8%)</f>
+        <v>211.68</v>
+      </c>
+      <c r="I17" s="22"/>
+      <c r="J17" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="22">
+        <f>B17*(1+8%)</f>
+        <v>211.68</v>
+      </c>
+      <c r="M17" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" s="22">
+        <f>B17*(1+8%)</f>
+        <v>211.68</v>
+      </c>
+      <c r="P17" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="20">
+        <f>B17*(1+8%)</f>
+        <v>211.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="E20" s="21" t="s">
+      <c r="B18" s="20">
+        <v>150</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="E18" s="20">
+        <v>150</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="20">
+        <f>B18*(1+7%)</f>
+        <v>160.5</v>
+      </c>
+      <c r="I18" s="22"/>
+      <c r="J18" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="22">
+        <f>B18*(1+7%)</f>
+        <v>160.5</v>
+      </c>
+      <c r="M18" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="22">
+        <f>B18*(1+7%)</f>
+        <v>160.5</v>
+      </c>
+      <c r="P18" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="20">
+        <f>B18*(1+7%)</f>
+        <v>160.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="20">
+        <v>900</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="20">
+        <v>900</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="22">
+        <f>B19*(1+5.5%)</f>
+        <v>949.5</v>
+      </c>
+      <c r="I19" s="22"/>
+      <c r="J19" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="22">
+        <f>B19*(1+5.5%)</f>
+        <v>949.5</v>
+      </c>
+      <c r="M19" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="22">
+        <f>B19*(1+5.5%)</f>
+        <v>949.5</v>
+      </c>
+      <c r="P19" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="22">
+        <f>B19*(1+5.5%)</f>
+        <v>949.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="24">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="19"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="19">
-        <v>196</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="22">
-        <f>B22+H20</f>
-        <v>196.08</v>
-      </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="16"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="19">
-        <v>150</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="16"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="19">
-        <v>900</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" s="16"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="19"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="19"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="20">
+        <v>200</v>
+      </c>
+      <c r="C20" s="21"/>
+      <c r="D20" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="20">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="22">
+        <v>200</v>
+      </c>
+      <c r="I20" s="22"/>
+      <c r="J20" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="22">
+        <v>0</v>
+      </c>
+      <c r="M20" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="N20" s="22">
+        <v>200</v>
+      </c>
+      <c r="P20" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q20" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="20">
+        <v>0</v>
+      </c>
+      <c r="C21" s="21"/>
+      <c r="D21" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="20">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="22">
+        <v>0</v>
+      </c>
+      <c r="I21" s="22"/>
+      <c r="J21" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="22">
+        <v>595</v>
+      </c>
+      <c r="M21" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" s="22">
+        <v>0</v>
+      </c>
+      <c r="P21" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q21" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="20">
+        <f>SUM(B17:B21)</f>
+        <v>1446</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="20">
+        <f>SUM(E17:E21)</f>
+        <v>1246</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="20">
+        <f>SUM(H17:H21)</f>
+        <v>1521.68</v>
+      </c>
+      <c r="I22" s="22"/>
+      <c r="J22" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="20">
+        <f>SUM(K17:K21)</f>
+        <v>1916.68</v>
+      </c>
+      <c r="M22" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="N22" s="22">
+        <f>SUM(N17:N21)</f>
+        <v>1521.68</v>
+      </c>
+      <c r="P22" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q22" s="20">
+        <f>SUM(Q17:Q21)</f>
+        <v>1321.68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="20">
+        <f>B16-B22</f>
+        <v>254</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="22">
+        <f>E16-E22</f>
+        <v>454</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="20">
+        <f>H16-H22</f>
+        <v>178.31999999999994</v>
+      </c>
+      <c r="I23" s="22"/>
+      <c r="J23" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" s="22">
+        <f>K16-K22</f>
+        <v>-46.679999999999836</v>
+      </c>
+      <c r="M23" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="22">
+        <f>N16-N22</f>
+        <v>348.32000000000016</v>
+      </c>
+      <c r="P23" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q23" s="22">
+        <f>Q16-Q22</f>
+        <v>548.32000000000016</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="20">
+        <f>B23</f>
+        <v>254</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="20">
+        <f>B24+E23</f>
+        <v>708</v>
+      </c>
+      <c r="F24" s="15"/>
+      <c r="G24" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="20">
+        <f>E24+H23</f>
+        <v>886.31999999999994</v>
+      </c>
+      <c r="I24" s="22"/>
+      <c r="J24" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="22">
+        <f>H24+K23</f>
+        <v>839.6400000000001</v>
+      </c>
+      <c r="M24" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="22">
+        <f>K24+N23</f>
+        <v>1187.9600000000003</v>
+      </c>
+      <c r="P24" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" s="22">
+        <f>N24+Q23</f>
+        <v>1736.2800000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C25" s="22"/>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26"/>
+      <c r="B26" s="14"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
-      <c r="B27" s="19"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="14"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
-      <c r="B28" s="19"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="14"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
-      <c r="B29" s="19"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="14"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
-      <c r="B30" s="19"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="14"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
-      <c r="B31" s="19"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="14"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
-      <c r="B32" s="19"/>
+      <c r="B32" s="14"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
-      <c r="B33" s="19"/>
+      <c r="B33" s="14"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
-      <c r="B34" s="19"/>
+      <c r="B34" s="14"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
-      <c r="B35" s="19"/>
+      <c r="B35" s="14"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
-      <c r="B36" s="19"/>
+      <c r="B36" s="14"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
-      <c r="B37" s="19"/>
+      <c r="B37" s="14"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
-      <c r="B38" s="19"/>
+      <c r="B38" s="14"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
-      <c r="B39" s="19"/>
+      <c r="B39" s="14"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
-      <c r="B40" s="19"/>
+      <c r="B40" s="14"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
@@ -795,12 +1196,17 @@
       <c r="A50" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="E15:G16"/>
+  <mergeCells count="6">
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
